--- a/source-data/Enerium_Ресурсы.xlsx
+++ b/source-data/Enerium_Ресурсы.xlsx
@@ -189,7 +189,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">edc1512a6ce29d74 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">967e3e12e5c6d4e3 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дар дня, бесплатный ряд пропуска, контракты эпической редкости и выше; Арена: суточный топ-100; Крафтовые боссы и эхо боссов биомов: победа возвращает часть Энериума призыва; Рецепт «Энериум из жилы» — с цикла V; Лавка Энериума</t>
+          <t xml:space="preserve">Дар дня, бесплатный ряд пропуска, контракты эпической редкости и выше; Арена: суточный топ-100; Призванные враги — боссы руин и городов, эхо боссов биомов: победа возвращает часть Энериума призыва; Рецепт «Энериум из жилы» — с цикла V; Лавка Энериума</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Контракты — главный источник; Босс биома — 10 %; за срабатывание столько ключей, какой цикл. С элит не падает; Сет «Менялы» — ключ с каждого N-го босса биома; Сундук странника и сундук крафтового босса — изредка; Стартовый набор в Лавке Энериума — один раз за игру</t>
+          <t xml:space="preserve">Контракты — главный источник; Босс биома — 10 %; за срабатывание столько ключей, какой цикл. С элит не падает; Сет «Менялы» — ключ с каждого N-го босса биома; Сундук странника и сундук призыва — изредка; Стартовый набор в Лавке Энериума — один раз за игру</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Мастерская форм» · один из шести ключей биома наугад; Ритуалы рабочих · Мастерская форм · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Крафтовый босс «Хатт-Уру, ловчий станции» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Мастерская форм» · один из шести ключей биома наугад; Ритуалы рабочих · Мастерская форм · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Призванный босс «Хатт-Уру, ловчий станции» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Мастерская форм» · один из шести ключей биома наугад; Ритуалы рабочих · Мастерская форм · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Крафтовый босс «Бур у стены» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Мастерская форм» · один из шести ключей биома наугад; Ритуалы рабочих · Мастерская форм · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Призванный босс «Бур у стены» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Мастерская форм» · один из шести ключей биома наугад; Ритуалы рабочих · Мастерская форм · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Крафтовый босс «Торбьёрн, ярл, пришедший за дровами» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Мастерская форм» · один из шести ключей биома наугад; Ритуалы рабочих · Мастерская форм · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Призванный Убер «Торбьёрн, ярл, пришедший за дровами» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Подземный лес» · один из шести ключей биома наугад; Ритуалы рабочих · Подземный лес · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Крафтовый босс «Хатт-Уру, ловчий станции» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Подземный лес» · один из шести ключей биома наугад; Ритуалы рабочих · Подземный лес · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Призванный босс «Хатт-Уру, ловчий станции» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Подземный лес» · один из шести ключей биома наугад; Ритуалы рабочих · Подземный лес · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Крафтовый босс «Бур у стены» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Подземный лес» · один из шести ключей биома наугад; Ритуалы рабочих · Подземный лес · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Призванный босс «Бур у стены» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Подземный лес» · один из шести ключей биома наугад; Ритуалы рабочих · Подземный лес · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Крафтовый босс «Торбьёрн, ярл, пришедший за дровами» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Подземный лес» · один из шести ключей биома наугад; Ритуалы рабочих · Подземный лес · от эпической редкости; Цепочка обучения — недостающие ключи, предложение; Призванный Убер «Торбьёрн, ярл, пришедший за дровами» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Хатт-Уру, ловчий станции» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Хатт-Уру, ловчий станции» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Бур у стены» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Бур у стены» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Торбьёрн, ярл, пришедший за дровами» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный Убер «Торбьёрн, ярл, пришедший за дровами» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="L169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Библиотека Улариона» · один из шести ключей биома наугад; Ритуалы рабочих · Библиотека Улариона · от эпической редкости; Крафтовый босс «Матка каменных жуков» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Библиотека Улариона» · один из шести ключей биома наугад; Ритуалы рабочих · Библиотека Улариона · от эпической редкости; Призванный босс «Матка каменных жуков» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M169" s="3" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Библиотека Улариона» · один из шести ключей биома наугад; Ритуалы рабочих · Библиотека Улариона · от эпической редкости; Крафтовый босс «Хродмар Гудок, что считал смены под завалом» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Библиотека Улариона» · один из шести ключей биома наугад; Ритуалы рабочих · Библиотека Улариона · от эпической редкости; Призванный босс «Хродмар Гудок, что считал смены под завалом» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="L173" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Библиотека Улариона» · один из шести ключей биома наугад; Ритуалы рабочих · Библиотека Улариона · от эпической редкости; Крафтовый босс «Лу-Ниэт, книжница башни» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Библиотека Улариона» · один из шести ключей биома наугад; Ритуалы рабочих · Библиотека Улариона · от эпической редкости; Призванный босс «Лу-Ниэт, книжница башни» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Библиотека Улариона» · один из шести ключей биома наугад; Ритуалы рабочих · Библиотека Улариона · от эпической редкости; Крафтовый босс «Огнемётный привод, у узких ворот» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Библиотека Улариона» · один из шести ключей биома наугад; Ритуалы рабочих · Библиотека Улариона · от эпической редкости; Призванный Убер «Огнемётный привод, у узких ворот» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Искусственный Стоун-Хейм» · один из шести ключей биома наугад; Ритуалы рабочих · Искусственный Стоун-Хейм · от эпической редкости; Крафтовый босс «Матка каменных жуков» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Искусственный Стоун-Хейм» · один из шести ключей биома наугад; Ритуалы рабочих · Искусственный Стоун-Хейм · от эпической редкости; Призванный босс «Матка каменных жуков» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="L181" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Искусственный Стоун-Хейм» · один из шести ключей биома наугад; Ритуалы рабочих · Искусственный Стоун-Хейм · от эпической редкости; Крафтовый босс «Хродмар Гудок, что считал смены под завалом» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Искусственный Стоун-Хейм» · один из шести ключей биома наугад; Ритуалы рабочих · Искусственный Стоун-Хейм · от эпической редкости; Призванный босс «Хродмар Гудок, что считал смены под завалом» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="L183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Искусственный Стоун-Хейм» · один из шести ключей биома наугад; Ритуалы рабочих · Искусственный Стоун-Хейм · от эпической редкости; Крафтовый босс «Лу-Ниэт, книжница башни» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Искусственный Стоун-Хейм» · один из шести ключей биома наугад; Ритуалы рабочих · Искусственный Стоун-Хейм · от эпической редкости; Призванный босс «Лу-Ниэт, книжница башни» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Искусственный Стоун-Хейм» · один из шести ключей биома наугад; Ритуалы рабочих · Искусственный Стоун-Хейм · от эпической редкости; Крафтовый босс «Огнемётный привод, у узких ворот» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Искусственный Стоун-Хейм» · один из шести ключей биома наугад; Ритуалы рабочих · Искусственный Стоун-Хейм · от эпической редкости; Призванный Убер «Огнемётный привод, у узких ворот» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="L202" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Лу-Ниэт, книжница башни» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Лу-Ниэт, книжница башни» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M202" s="3" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="L218" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Хродмар Гудок, что считал смены под завалом» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Хродмар Гудок, что считал смены под завалом» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Матка каменных жуков» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Матка каменных жуков» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="L253" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Огнемётный привод, у узких ворот» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный Убер «Огнемётный привод, у узких ворот» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M253" s="3" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="L321" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Кузня» · один из шести ключей биома наугад; Ритуалы рабочих · Кузня · от эпической редкости; Крафтовый босс «Таран у ворот» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Кузня» · один из шести ключей биома наугад; Ритуалы рабочих · Кузня · от эпической редкости; Призванный босс «Таран у ворот» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M321" s="3" t="inlineStr">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="L322" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Кузня» · один из шести ключей биома наугад; Ритуалы рабочих · Кузня · от эпической редкости; Крафтовый босс «Пламя над курганом» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Кузня» · один из шести ключей биома наугад; Ритуалы рабочих · Кузня · от эпической редкости; Призванный босс «Пламя над курганом» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M322" s="3" t="inlineStr">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="L324" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Кузня» · один из шести ключей биома наугад; Ритуалы рабочих · Кузня · от эпической редкости; Крафтовый босс «Сеймур, учитель» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Кузня» · один из шести ключей биома наугад; Ритуалы рабочих · Кузня · от эпической редкости; Призванный Убер «Сеймур, учитель» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M324" s="3" t="inlineStr">
@@ -20307,7 +20307,7 @@
       </c>
       <c r="L331" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Арена, где бой не кончался» · один из шести ключей биома наугад; Ритуалы рабочих · Арена, где бой не кончался · от эпической редкости; Крафтовый босс «Таран у ворот» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Арена, где бой не кончался» · один из шести ключей биома наугад; Ритуалы рабочих · Арена, где бой не кончался · от эпической редкости; Призванный босс «Таран у ворот» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M331" s="3" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="L332" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Арена, где бой не кончался» · один из шести ключей биома наугад; Ритуалы рабочих · Арена, где бой не кончался · от эпической редкости; Крафтовый босс «Пламя над курганом» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Арена, где бой не кончался» · один из шести ключей биома наугад; Ритуалы рабочих · Арена, где бой не кончался · от эпической редкости; Призванный босс «Пламя над курганом» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M332" s="3" t="inlineStr">
@@ -20493,7 +20493,7 @@
       </c>
       <c r="L334" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Арена, где бой не кончался» · один из шести ключей биома наугад; Ритуалы рабочих · Арена, где бой не кончался · от эпической редкости; Крафтовый босс «Сеймур, учитель» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Арена, где бой не кончался» · один из шести ключей биома наугад; Ритуалы рабочих · Арена, где бой не кончался · от эпической редкости; Призванный Убер «Сеймур, учитель» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M334" s="3" t="inlineStr">
@@ -21517,7 +21517,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -21584,7 +21584,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -21614,7 +21614,7 @@
       </c>
       <c r="L352" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Зверь без всадника» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Зверь без всадника» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M352" s="3" t="inlineStr">
@@ -22514,7 +22514,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="L368" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Пламя над курганом» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Пламя над курганом» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M368" s="3" t="inlineStr">
@@ -23511,7 +23511,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -23578,7 +23578,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -23608,7 +23608,7 @@
       </c>
       <c r="L384" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Таран у ворот» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Таран у ворот» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M384" s="3" t="inlineStr">
@@ -24508,7 +24508,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -24575,7 +24575,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -24605,7 +24605,7 @@
       </c>
       <c r="L400" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Кузнец для тех, кто не придёт» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Кузнец для тех, кто не придёт» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M400" s="3" t="inlineStr">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -25758,7 +25758,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="L419" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Сеймур, учитель» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный Убер «Сеймур, учитель» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M419" s="3" t="inlineStr">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="L477" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Залы у водопадов» · один из шести ключей биома наугад; Ритуалы рабочих · Залы у водопадов · от эпической редкости; Крафтовый босс «Спящий под маяком» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Залы у водопадов» · один из шести ключей биома наугад; Ритуалы рабочих · Залы у водопадов · от эпической редкости; Призванный босс «Спящий под маяком» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M477" s="3" t="inlineStr">
@@ -29238,7 +29238,7 @@
       </c>
       <c r="L479" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Залы у водопадов» · один из шести ключей биома наугад; Ритуалы рабочих · Залы у водопадов · от эпической редкости; Крафтовый босс «Смотритель шлюза» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Залы у водопадов» · один из шести ключей биома наугад; Ритуалы рабочих · Залы у водопадов · от эпической редкости; Призванный босс «Смотритель шлюза» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M479" s="3" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="L480" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Залы у водопадов» · один из шести ключей биома наугад; Ритуалы рабочих · Залы у водопадов · от эпической редкости; Крафтовый босс «Страж арки» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Залы у водопадов» · один из шести ключей биома наугад; Ритуалы рабочих · Залы у водопадов · от эпической редкости; Призванный Убер «Страж арки» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M480" s="3" t="inlineStr">
@@ -29744,7 +29744,7 @@
       </c>
       <c r="L487" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Город суда» · один из шести ключей биома наугад; Ритуалы рабочих · Город суда · от эпической редкости; Крафтовый босс «Спящий под маяком» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Город суда» · один из шести ключей биома наугад; Ритуалы рабочих · Город суда · от эпической редкости; Призванный босс «Спящий под маяком» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M487" s="3" t="inlineStr">
@@ -29868,7 +29868,7 @@
       </c>
       <c r="L489" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Город суда» · один из шести ключей биома наугад; Ритуалы рабочих · Город суда · от эпической редкости; Крафтовый босс «Смотритель шлюза» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Город суда» · один из шести ключей биома наугад; Ритуалы рабочих · Город суда · от эпической редкости; Призванный босс «Смотритель шлюза» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M489" s="3" t="inlineStr">
@@ -29930,7 +29930,7 @@
       </c>
       <c r="L490" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Город суда» · один из шести ключей биома наугад; Ритуалы рабочих · Город суда · от эпической редкости; Крафтовый босс «Страж арки» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Город суда» · один из шести ключей биома наугад; Ритуалы рабочих · Город суда · от эпической редкости; Призванный Убер «Страж арки» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M490" s="3" t="inlineStr">
@@ -31078,7 +31078,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -31145,7 +31145,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -31175,7 +31175,7 @@
       </c>
       <c r="L510" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Меда-Ус, хранительница воды» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Меда-Ус, хранительница воды» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M510" s="3" t="inlineStr">
@@ -32075,7 +32075,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
@@ -32142,7 +32142,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -32172,7 +32172,7 @@
       </c>
       <c r="L526" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Спящий под маяком» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Спящий под маяком» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M526" s="3" t="inlineStr">
@@ -33072,7 +33072,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
@@ -33139,7 +33139,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="L542" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Жребиемёт» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Жребиемёт» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M542" s="3" t="inlineStr">
@@ -34069,7 +34069,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -34136,7 +34136,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
@@ -34166,7 +34166,7 @@
       </c>
       <c r="L558" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Смотритель шлюза» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Смотритель шлюза» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M558" s="3" t="inlineStr">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
@@ -35349,7 +35349,7 @@
       </c>
       <c r="L577" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Страж арки» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный Убер «Страж арки» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M577" s="3" t="inlineStr">
@@ -38841,7 +38841,7 @@
       </c>
       <c r="L638" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Зал часов» · один из шести ключей биома наугад; Ритуалы рабочих · Зал часов · от эпической редкости; Крафтовый босс «Зверь в прыжке» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Зал часов» · один из шести ключей биома наугад; Ритуалы рабочих · Зал часов · от эпической редкости; Призванный босс «Зверь в прыжке» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M638" s="3" t="inlineStr">
@@ -38903,7 +38903,7 @@
       </c>
       <c r="L639" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Зал часов» · один из шести ключей биома наугад; Ритуалы рабочих · Зал часов · от эпической редкости; Крафтовый босс «Ведда-Ор, что спускала на верёвке» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Зал часов» · один из шести ключей биома наугад; Ритуалы рабочих · Зал часов · от эпической редкости; Призванный босс «Ведда-Ор, что спускала на верёвке» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M639" s="3" t="inlineStr">
@@ -39027,7 +39027,7 @@
       </c>
       <c r="L641" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Зал часов» · один из шести ключей биома наугад; Ритуалы рабочих · Зал часов · от эпической редкости; Крафтовый босс «Та, что ждёт» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Зал часов» · один из шести ключей биома наугад; Ритуалы рабочих · Зал часов · от эпической редкости; Призванный босс «Та, что ждёт» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M641" s="3" t="inlineStr">
@@ -39089,7 +39089,7 @@
       </c>
       <c r="L642" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Зал часов» · один из шести ключей биома наугад; Ритуалы рабочих · Зал часов · от эпической редкости; Крафтовый босс «Селестина, первая в архиве Доводов» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Зал часов» · один из шести ключей биома наугад; Ритуалы рабочих · Зал часов · от эпической редкости; Призванный Убер «Селестина, первая в архиве Доводов» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M642" s="3" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="L648" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Лабиринт у воронки» · один из шести ключей биома наугад; Ритуалы рабочих · Лабиринт у воронки · от эпической редкости; Крафтовый босс «Зверь в прыжке» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Лабиринт у воронки» · один из шести ключей биома наугад; Ритуалы рабочих · Лабиринт у воронки · от эпической редкости; Призванный босс «Зверь в прыжке» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M648" s="3" t="inlineStr">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="L649" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Лабиринт у воронки» · один из шести ключей биома наугад; Ритуалы рабочих · Лабиринт у воронки · от эпической редкости; Крафтовый босс «Ведда-Ор, что спускала на верёвке» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Лабиринт у воронки» · один из шести ключей биома наугад; Ритуалы рабочих · Лабиринт у воронки · от эпической редкости; Призванный босс «Ведда-Ор, что спускала на верёвке» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M649" s="3" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="L651" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Лабиринт у воронки» · один из шести ключей биома наугад; Ритуалы рабочих · Лабиринт у воронки · от эпической редкости; Крафтовый босс «Та, что ждёт» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Лабиринт у воронки» · один из шести ключей биома наугад; Ритуалы рабочих · Лабиринт у воронки · от эпической редкости; Призванный босс «Та, что ждёт» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M651" s="3" t="inlineStr">
@@ -39719,7 +39719,7 @@
       </c>
       <c r="L652" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Лабиринт у воронки» · один из шести ключей биома наугад; Ритуалы рабочих · Лабиринт у воронки · от эпической редкости; Крафтовый босс «Селестина, первая в архиве Доводов» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Лабиринт у воронки» · один из шести ключей биома наугад; Ритуалы рабочих · Лабиринт у воронки · от эпической редкости; Призванный Убер «Селестина, первая в архиве Доводов» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M652" s="3" t="inlineStr">
@@ -40805,7 +40805,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
@@ -40872,7 +40872,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="L671" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Ведда-Ор, что спускала на верёвке» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Ведда-Ор, что спускала на верёвке» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M671" s="3" t="inlineStr">
@@ -41802,7 +41802,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
@@ -41869,7 +41869,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
@@ -41899,7 +41899,7 @@
       </c>
       <c r="L687" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Тень полудня» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Тень полудня» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M687" s="3" t="inlineStr">
@@ -42799,7 +42799,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
@@ -42866,7 +42866,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
@@ -42896,7 +42896,7 @@
       </c>
       <c r="L703" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Погонщик, что опоздал» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Погонщик, что опоздал» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M703" s="3" t="inlineStr">
@@ -43796,7 +43796,7 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
@@ -43863,7 +43863,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
@@ -43893,7 +43893,7 @@
       </c>
       <c r="L719" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Та, что ждёт» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Та, что ждёт» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M719" s="3" t="inlineStr">
@@ -44793,7 +44793,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
@@ -44860,7 +44860,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
@@ -44890,7 +44890,7 @@
       </c>
       <c r="L735" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Зверь в прыжке» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Зверь в прыжке» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M735" s="3" t="inlineStr">
@@ -45976,7 +45976,7 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
@@ -46043,7 +46043,7 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
@@ -46073,7 +46073,7 @@
       </c>
       <c r="L754" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Селестина, первая в архиве Доводов» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный Убер «Селестина, первая в архиве Доводов» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M754" s="3" t="inlineStr">
@@ -49736,7 +49736,7 @@
       </c>
       <c r="L818" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Литейная богов» · один из шести ключей биома наугад; Ритуалы рабочих · Литейная богов · от эпической редкости; Крафтовый босс «Первый из поднявшихся» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Литейная богов» · один из шести ключей биома наугад; Ритуалы рабочих · Литейная богов · от эпической редкости; Призванный Убер «Первый из поднявшихся» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M818" s="3" t="inlineStr">
@@ -49870,7 +49870,7 @@
       </c>
       <c r="L820" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Литейная богов» · один из шести ключей биома наугад; Ритуалы рабочих · Литейная богов · от эпической редкости; Крафтовый босс «Стоящий лицом к работе» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Литейная богов» · один из шести ключей биома наугад; Ритуалы рабочих · Литейная богов · от эпической редкости; Призванный босс «Стоящий лицом к работе» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M820" s="3" t="inlineStr">
@@ -50004,7 +50004,7 @@
       </c>
       <c r="L822" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Литейная богов» · один из шести ключей биома наугад; Ритуалы рабочих · Литейная богов · от эпической редкости; Крафтовый босс «Учитель у Оболочки» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Литейная богов» · один из шести ключей биома наугад; Ритуалы рабочих · Литейная богов · от эпической редкости; Призванный босс «Учитель у Оболочки» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M822" s="3" t="inlineStr">
@@ -50416,7 +50416,7 @@
       </c>
       <c r="L828" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Сердцевина» · один из шести ключей биома наугад; Ритуалы рабочих · Сердцевина · от эпической редкости; Крафтовый босс «Первый из поднявшихся» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Сердцевина» · один из шести ключей биома наугад; Ритуалы рабочих · Сердцевина · от эпической редкости; Призванный Убер «Первый из поднявшихся» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M828" s="3" t="inlineStr">
@@ -50550,7 +50550,7 @@
       </c>
       <c r="L830" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Сердцевина» · один из шести ключей биома наугад; Ритуалы рабочих · Сердцевина · от эпической редкости; Крафтовый босс «Стоящий лицом к работе» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Сердцевина» · один из шести ключей биома наугад; Ритуалы рабочих · Сердцевина · от эпической редкости; Призванный босс «Стоящий лицом к работе» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M830" s="3" t="inlineStr">
@@ -50684,7 +50684,7 @@
       </c>
       <c r="L832" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Любая элита биома «Сердцевина» · один из шести ключей биома наугад; Ритуалы рабочих · Сердцевина · от эпической редкости; Крафтовый босс «Учитель у Оболочки» · Эхо · ключи своего ремесла</t>
+          <t xml:space="preserve">Любая элита биома «Сердцевина» · один из шести ключей биома наугад; Ритуалы рабочих · Сердцевина · от эпической редкости; Призванный босс «Учитель у Оболочки» · Эхо · ключи своего ремесла</t>
         </is>
       </c>
       <c r="M832" s="3" t="inlineStr">
@@ -51860,7 +51860,7 @@
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
@@ -51932,7 +51932,7 @@
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
@@ -51962,7 +51962,7 @@
       </c>
       <c r="L851" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Несостоявшаяся отливка» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Несостоявшаяся отливка» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M851" s="3" t="inlineStr">
@@ -52937,7 +52937,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
@@ -53009,7 +53009,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
@@ -53039,7 +53039,7 @@
       </c>
       <c r="L867" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Стоящий лицом к работе» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Стоящий лицом к работе» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M867" s="3" t="inlineStr">
@@ -54014,7 +54014,7 @@
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
@@ -54086,7 +54086,7 @@
       </c>
       <c r="E883" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
@@ -54116,7 +54116,7 @@
       </c>
       <c r="L883" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Учитель у Оболочки» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный босс «Учитель у Оболочки» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M883" s="3" t="inlineStr">
@@ -55292,7 +55292,7 @@
       </c>
       <c r="E901" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
@@ -55364,7 +55364,7 @@
       </c>
       <c r="E902" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="F902" t="inlineStr">
@@ -55394,7 +55394,7 @@
       </c>
       <c r="L902" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Крафтовый босс «Первый из поднявшихся» · Эхо · 1 за победу</t>
+          <t xml:space="preserve">Призванный Убер «Первый из поднявшихся» · Эхо · 1 за победу</t>
         </is>
       </c>
       <c r="M902" s="3" t="inlineStr">
@@ -58922,7 +58922,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Трофей крафтового босса</t>
+          <t xml:space="preserve">Трофей босса руины или города</t>
         </is>
       </c>
       <c r="C7">
@@ -59087,7 +59087,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Призыв крафтового босса</t>
+          <t xml:space="preserve">Призыв босса руины или города</t>
         </is>
       </c>
       <c r="C18">

--- a/source-data/Enerium_Ресурсы.xlsx
+++ b/source-data/Enerium_Ресурсы.xlsx
@@ -177,7 +177,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -189,7 +189,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">967e3e12e5c6d4e3 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">ad08ab6673f81a3d — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -304,8 +304,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Контракты — главный источник; Босс биома — 10 %; за срабатывание столько ключей, какой цикл. С элит не падает; Сет «Менялы» — ключ с каждого N-го босса биома; Сундук странника и сундук призыва — изредка; Стартовый набор в Лавке Энериума — один раз за игру</t>
+          <t xml:space="preserve">Контракты — главный источник; Босс биома — 10 %; за срабатывание столько ключей, какой цикл. С элит не падает; Сет «Менялы» — ключ с каждого N-го босса биома; Сундук странника и сундук призыва — изредка; Разовые наборы в Лавке Энериума — каждый один раз за игру</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
